--- a/config/lables2.xlsx
+++ b/config/lables2.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:3">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>25</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:3">
       <c r="A3" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>25</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:3">
       <c r="A4" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>25</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:3">
       <c r="A5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>25</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:3">
       <c r="A6" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>25</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:3">
       <c r="A7" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>25</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:3">
       <c r="A8" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>25</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:3">
       <c r="A9" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>25</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:3">
       <c r="A10" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>25</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:3">
       <c r="A11" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>25</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:3">
       <c r="A12" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>25</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:3">
       <c r="A13" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>25</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:3">
       <c r="A14" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>25</v>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:3">
       <c r="A15" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>25</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:3">
       <c r="A16" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>31</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:3">
       <c r="A17" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>31</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:3">
       <c r="A18" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>37</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:3">
       <c r="A19" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1">
         <v>43</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:3">
       <c r="A20" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>49</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:3">
       <c r="A21" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
         <v>55</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:3">
       <c r="A22" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>55</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:3">
       <c r="A23" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>61</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:3">
       <c r="A24" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>67</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:3">
       <c r="A25" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>73</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:3">
       <c r="A26" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
         <v>79</v>
